--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>86.10454948591105</v>
+        <v>13.99198929146055</v>
       </c>
       <c r="D2" t="n">
-        <v>85.94880807172372</v>
+        <v>13.9666813116551</v>
       </c>
       <c r="E2" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F2" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.79817758143464</v>
+        <v>9.22970385698313</v>
       </c>
       <c r="D3" t="n">
-        <v>57.00597267683477</v>
+        <v>9.263470559985651</v>
       </c>
       <c r="E3" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F3" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.97283434607864</v>
+        <v>7.633085581237779</v>
       </c>
       <c r="D4" t="n">
-        <v>47.06990301698319</v>
+        <v>7.648859240259768</v>
       </c>
       <c r="E4" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F4" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.45806226939728</v>
+        <v>3.974435118777058</v>
       </c>
       <c r="D5" t="n">
-        <v>24.6096132150199</v>
+        <v>3.999062147440734</v>
       </c>
       <c r="E5" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F5" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.74786965150216</v>
+        <v>2.721528818369101</v>
       </c>
       <c r="D6" t="n">
-        <v>16.96756340096697</v>
+        <v>2.757229052657132</v>
       </c>
       <c r="E6" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F6" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.91807819297679</v>
+        <v>3.236687706358728</v>
       </c>
       <c r="D7" t="n">
-        <v>19.61792537127566</v>
+        <v>3.187912872832295</v>
       </c>
       <c r="E7" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F7" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>10.03087446855962</v>
+        <v>1.630017101140938</v>
       </c>
       <c r="D8" t="n">
-        <v>10.30246926769731</v>
+        <v>1.674151256000814</v>
       </c>
       <c r="E8" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F8" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>5.88340146478378</v>
+        <v>0.9560527380273643</v>
       </c>
       <c r="D9" t="n">
-        <v>5.660000457663703</v>
+        <v>0.9197500743703517</v>
       </c>
       <c r="E9" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F9" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.54531073415499</v>
+        <v>6.426112994300186</v>
       </c>
       <c r="D10" t="n">
-        <v>40.27135378213155</v>
+        <v>6.544094989596377</v>
       </c>
       <c r="E10" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F10" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>54.8118181159731</v>
+        <v>8.90692044384563</v>
       </c>
       <c r="D11" t="n">
-        <v>54.50201513557156</v>
+        <v>8.85657745953038</v>
       </c>
       <c r="E11" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F11" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.21361632114532</v>
+        <v>5.234712652186115</v>
       </c>
       <c r="D12" t="n">
-        <v>32.93631747537829</v>
+        <v>5.352151589748972</v>
       </c>
       <c r="E12" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F12" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>56.19313658896784</v>
+        <v>9.131384695707274</v>
       </c>
       <c r="D13" t="n">
-        <v>55.9276180817518</v>
+        <v>9.088237938284669</v>
       </c>
       <c r="E13" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F13" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>19.06016166788169</v>
+        <v>3.097276271030776</v>
       </c>
       <c r="D14" t="n">
-        <v>19.67820966444276</v>
+        <v>3.197709070471949</v>
       </c>
       <c r="E14" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F14" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>44.23393664006593</v>
+        <v>7.188014704010714</v>
       </c>
       <c r="D15" t="n">
-        <v>44.24454499745199</v>
+        <v>7.189738562085949</v>
       </c>
       <c r="E15" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F15" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>69.19411524142835</v>
+        <v>11.24404372673211</v>
       </c>
       <c r="D16" t="n">
-        <v>68.96771025798557</v>
+        <v>11.20725291692266</v>
       </c>
       <c r="E16" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F16" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>53.25351653871825</v>
+        <v>8.653696437541717</v>
       </c>
       <c r="D17" t="n">
-        <v>53.13165470586949</v>
+        <v>8.633893889703794</v>
       </c>
       <c r="E17" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F17" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>54.31135677385937</v>
+        <v>8.825595475752147</v>
       </c>
       <c r="D18" t="n">
-        <v>54.30361072200756</v>
+        <v>8.824336742326228</v>
       </c>
       <c r="E18" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F18" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>67.49198955441999</v>
+        <v>10.96744830259325</v>
       </c>
       <c r="D19" t="n">
-        <v>67.38633191572752</v>
+        <v>10.95027893630572</v>
       </c>
       <c r="E19" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F19" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>72.1556811227468</v>
+        <v>11.72529818244636</v>
       </c>
       <c r="D20" t="n">
-        <v>72.01588983971826</v>
+        <v>11.70258209895422</v>
       </c>
       <c r="E20" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F20" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>44.30792102508189</v>
+        <v>7.200037166575807</v>
       </c>
       <c r="D21" t="n">
-        <v>43.64603243505272</v>
+        <v>7.092480270696067</v>
       </c>
       <c r="E21" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F21" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>32.39285960161465</v>
+        <v>5.26383968526238</v>
       </c>
       <c r="D22" t="n">
-        <v>31.6699626820301</v>
+        <v>5.146368935829892</v>
       </c>
       <c r="E22" t="n">
-        <v>21.37413388167115</v>
+        <v>3.473296755771563</v>
       </c>
       <c r="F22" t="n">
-        <v>21.27675285854293</v>
+        <v>3.457472339513227</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
